--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487633_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487633_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.174</v>
+        <v>0.8616</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4683</v>
+        <v>3.1605</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2943</v>
+        <v>-2.2988</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8325</v>
+        <v>3.1177</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9287</v>
+        <v>3.106</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.7611</v>
+        <v>0.0117</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7495000000000001</v>
+        <v>4.4044</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9979</v>
+        <v>3.831</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.2484</v>
+        <v>0.5734</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5819</v>
+        <v>-1.2867</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0692</v>
+        <v>-0.725</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.5127</v>
+        <v>-0.5617</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.7463</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3284</v>
+        <v>-3.2985</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9569</v>
+        <v>-0.1217</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3174</v>
+        <v>-0.3931</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.2714</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7958</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7298</v>
+        <v>2.4477</v>
       </c>
       <c r="X2" t="n">
-        <v>0.066</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6554</v>
+        <v>0.6042</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8997</v>
+        <v>2.5268</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2443</v>
+        <v>-1.9226</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1177</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>3.106</v>
+        <v>2.9494</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0117</v>
+        <v>-2.1567</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4044</v>
+        <v>3.3755</v>
       </c>
       <c r="K3" t="n">
-        <v>3.831</v>
+        <v>3.2131</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5734</v>
+        <v>0.1624</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2867</v>
+        <v>-2.5827</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.725</v>
+        <v>-0.2637</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5617</v>
+        <v>-2.3191</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.1344</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q3" t="n">
         <v>-3.2985</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3279</v>
+        <v>-0.6858</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6539</v>
+        <v>-0.5143</v>
       </c>
       <c r="U3" t="n">
-        <v>0.326</v>
+        <v>-0.1716</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.4077</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4477</v>
+        <v>2.9641</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4477</v>
+        <v>0.4436</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3434</v>
+        <v>0.3802</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2661</v>
+        <v>1.3286</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9226</v>
+        <v>-0.9484</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7927999999999999</v>
+        <v>-0.8325</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9494</v>
+        <v>1.9287</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.1567</v>
+        <v>-2.7611</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3755</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2131</v>
+        <v>1.9979</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1624</v>
+        <v>-1.2484</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5827</v>
+        <v>-1.5819</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2637</v>
+        <v>-0.0692</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.3191</v>
+        <v>-1.5127</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.9105</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2985</v>
+        <v>-2.3284</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9466</v>
+        <v>0.1632</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.775</v>
+        <v>0.1777</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1716</v>
+        <v>-0.0145</v>
       </c>
       <c r="V4" t="n">
-        <v>3.4077</v>
+        <v>2.7958</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9641</v>
+        <v>2.7298</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4436</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6162</v>
+        <v>-0.4889</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9013</v>
+        <v>-0.8012</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2851</v>
+        <v>0.3124</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3798</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1516</v>
+        <v>0.279</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1335</v>
+        <v>0.2336</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PASTOR LOPEZ</t>
+          <t>I. GARCIA BENITO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1806</v>
+        <v>-1.6911</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8272</v>
+        <v>-1.1622</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3534</v>
+        <v>-0.529</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.22</v>
+        <v>0.4149</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2144</v>
+        <v>-0.0428</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0056</v>
+        <v>0.4577</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5849</v>
+        <v>-0.035</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5849</v>
+        <v>0.0412</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.0762</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.635</v>
+        <v>0.4498</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6294</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0056</v>
+        <v>0.5339</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3881</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.3582</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3881</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4547</v>
+        <v>0.4761</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2423</v>
+        <v>0.231</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2124</v>
+        <v>0.2451</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. GARCIA BENITO</t>
+          <t>A. PASTOR LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2823</v>
+        <v>-1.9987</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5626</v>
+        <v>-0.7271</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7198</v>
+        <v>-1.2716</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4149</v>
+        <v>-1.22</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0428</v>
+        <v>-1.2144</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4577</v>
+        <v>-0.0056</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.035</v>
+        <v>-0.5849</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0412</v>
+        <v>-0.5849</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0762</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4498</v>
+        <v>-0.635</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.6294</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5339</v>
+        <v>-0.0056</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3582</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1151</v>
+        <v>-0.2728</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1694</v>
+        <v>-0.1422</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0543</v>
+        <v>-0.1307</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2239</v>
+        <v>-0.894</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4162</v>
+        <v>-3.1198</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0966</v>
+        <v>-2.6367</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3196</v>
+        <v>-0.4831</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6232</v>
@@ -1078,13 +1078,13 @@
         <v>0.5821</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4309</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0442</v>
+        <v>0.5041</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3867</v>
+        <v>0.2232</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2239</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7978</v>
+        <v>-3.8801</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0049</v>
+        <v>-1.3052</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7929</v>
+        <v>-2.5749</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7811</v>
@@ -1156,13 +1156,13 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0722</v>
+        <v>-0.1545</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4262</v>
+        <v>0.1259</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4984</v>
+        <v>-0.2804</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1683</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BALDAN MARTÍN</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8576</v>
+        <v>-4.0076</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3854</v>
+        <v>-1.7867</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4722</v>
+        <v>-2.2209</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-1.4782</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.856</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2319</v>
+        <v>-0.6222</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5649</v>
+        <v>1.7889</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6055</v>
+        <v>-0.5808</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0406</v>
+        <v>2.3697</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4175</v>
+        <v>-3.2672</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.145</v>
+        <v>-0.2752</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2725</v>
+        <v>-2.992</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3284</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3284</v>
+        <v>-3.2985</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5529</v>
+        <v>-0.461</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2259</v>
+        <v>-0.2771</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3271</v>
+        <v>-0.1839</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0997</v>
+        <v>0.066</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3818</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6994</v>
+        <v>-4.2747</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5875</v>
+        <v>-2.7691</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1119</v>
+        <v>-1.5057</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4782</v>
+        <v>-2.8839</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.856</v>
+        <v>0.8115</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6222</v>
+        <v>-3.6954</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7889</v>
+        <v>-0.6525</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5808</v>
+        <v>0.0453</v>
       </c>
       <c r="L11" t="n">
-        <v>2.3697</v>
+        <v>-0.6979</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.2672</v>
+        <v>-2.2313</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2752</v>
+        <v>0.7662</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.992</v>
+        <v>-2.9975</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1344</v>
+        <v>-4.0747</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2985</v>
+        <v>-4.8508</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1527</v>
+        <v>0.5182</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0779</v>
+        <v>0.2865</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.2316</v>
       </c>
       <c r="V11" t="n">
-        <v>0.066</v>
+        <v>2.1657</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X11" t="n">
-        <v>0.066</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>M. BALDAN MARTÍN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7263</v>
+        <v>-4.3125</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0298</v>
+        <v>-1.7858</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6964</v>
+        <v>-2.5267</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8839</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8115</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.6954</v>
+        <v>-0.2319</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6525</v>
+        <v>-0.5649</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0453</v>
+        <v>-0.6055</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6979</v>
+        <v>0.0406</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2313</v>
+        <v>-0.4175</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7662</v>
+        <v>-0.145</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.9975</v>
+        <v>-0.2725</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.0747</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.8508</v>
+        <v>-2.3284</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7761</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.06660000000000001</v>
+        <v>1.098</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0258</v>
+        <v>0.8255</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0409</v>
+        <v>0.2725</v>
       </c>
       <c r="V12" t="n">
-        <v>2.1657</v>
+        <v>-2.0997</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4477</v>
+        <v>0.2821</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2821</v>
+        <v>-2.3818</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.9462</v>
+        <v>-6.1197</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9131</v>
+        <v>-3.4136</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0332</v>
+        <v>-2.7061</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7414</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1534</v>
+        <v>0.98</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2146</v>
+        <v>0.7141</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0612</v>
+        <v>0.2658</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4477</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-28.3498</v>
+        <v>-28.0471</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.674299999999999</v>
+        <v>-9.371699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.6755</v>
+        <v>-18.6754</v>
       </c>
       <c r="G14" t="n">
         <v>-10.5971</v>
@@ -1522,10 +1522,10 @@
         <v>5.575100000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>4.712699999999998</v>
+        <v>4.7127</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8622999999999998</v>
+        <v>0.8623000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-16.1721</v>
@@ -1546,16 +1546,16 @@
         <v>6.791199999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2431</v>
+        <v>2.546</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4691</v>
+        <v>1.7717</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7743</v>
+        <v>0.7739</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3776999999999999</v>
+        <v>0.3777000000000004</v>
       </c>
       <c r="W14" t="n">
         <v>10.446</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.479200000000001</v>
+        <v>10.1099</v>
       </c>
       <c r="E15" t="n">
-        <v>7.9262</v>
+        <v>8.1264</v>
       </c>
       <c r="F15" t="n">
-        <v>1.553</v>
+        <v>1.9835</v>
       </c>
       <c r="G15" t="n">
         <v>6.7468</v>
@@ -1624,13 +1624,13 @@
         <v>3.6866</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4915</v>
+        <v>-0.8608</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9691</v>
+        <v>-0.7689</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5224</v>
+        <v>-0.092</v>
       </c>
       <c r="V15" t="n">
         <v>0.5373</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3029</v>
+        <v>6.7728</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8608</v>
+        <v>4.061</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4421</v>
+        <v>2.7118</v>
       </c>
       <c r="G16" t="n">
         <v>4.1391</v>
@@ -1702,13 +1702,13 @@
         <v>2.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0004</v>
+        <v>-0.5305</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6539</v>
+        <v>-0.4537</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3465</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>1.2239</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.7496</v>
+        <v>6.1016</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1651</v>
+        <v>4.4654</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5845</v>
+        <v>1.6362</v>
       </c>
       <c r="G17" t="n">
         <v>4.1614</v>
@@ -1780,13 +1780,13 @@
         <v>3.1045</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7342</v>
+        <v>-0.3822</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2894</v>
+        <v>0.0109</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4448</v>
+        <v>-0.3931</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7821</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.6346</v>
+        <v>3.5223</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6974</v>
+        <v>2.3971</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9372</v>
+        <v>1.1252</v>
       </c>
       <c r="G18" t="n">
         <v>1.1075</v>
@@ -1858,13 +1858,13 @@
         <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2788</v>
+        <v>-0.3911</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1828</v>
+        <v>-0.1175</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4616</v>
+        <v>-0.2736</v>
       </c>
       <c r="V18" t="n">
         <v>1.8358</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.0968</v>
+        <v>2.8877</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9007</v>
+        <v>1.8006</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1961</v>
+        <v>1.0871</v>
       </c>
       <c r="G19" t="n">
         <v>0.7272999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>3.1045</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7158</v>
+        <v>0.5067</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0471</v>
+        <v>-0.1472</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7629</v>
+        <v>0.6539</v>
       </c>
       <c r="V19" t="n">
         <v>0.4895</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5173</v>
+        <v>1.7058</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0106</v>
+        <v>1.3109</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.3948</v>
       </c>
       <c r="G20" t="n">
         <v>0.554</v>
@@ -2014,13 +2014,13 @@
         <v>2.3284</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3692</v>
+        <v>0.5577</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0258</v>
+        <v>0.3261</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3435</v>
+        <v>0.2316</v>
       </c>
       <c r="V20" t="n">
         <v>1.1761</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0134</v>
+        <v>1.1924</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6997</v>
+        <v>1.7998</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6863</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.9807</v>
@@ -2092,13 +2092,13 @@
         <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2375</v>
+        <v>-1.0585</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6057</v>
+        <v>-0.5056</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6319</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2821</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8971</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>1.041</v>
+        <v>0.7407</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1439</v>
+        <v>-0.0104</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1291</v>
@@ -2170,13 +2170,13 @@
         <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2187</v>
+        <v>0.0519</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4856</v>
+        <v>0.1853</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2669</v>
+        <v>-0.1335</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3567</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2848</v>
+        <v>0.5766</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3525</v>
+        <v>0.3482</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0677</v>
+        <v>0.2285</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1133</v>
@@ -2248,13 +2248,13 @@
         <v>2.3284</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0372</v>
+        <v>-0.1758</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5933</v>
+        <v>0.1074</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4439</v>
+        <v>-0.2832</v>
       </c>
       <c r="V23" t="n">
         <v>0.5373</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4931</v>
+        <v>-0.8061</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4254</v>
+        <v>-1.7771</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0678</v>
+        <v>0.971</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4156</v>
+        <v>-0.9457</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8594</v>
+        <v>-0.6599</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5561</v>
+        <v>-0.2858</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8862</v>
+        <v>-0.7167</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.0308</v>
+        <v>0.103</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1446</v>
+        <v>-0.8196</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5294</v>
+        <v>-0.229</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1714</v>
+        <v>-0.7629</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7008</v>
+        <v>0.5339</v>
       </c>
       <c r="P24" t="n">
-        <v>3.2985</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R24" t="n">
-        <v>3.2985</v>
+        <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4015</v>
+        <v>0.1396</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1787</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2228</v>
+        <v>0.2299</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.7776</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.0597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.0063</v>
+        <v>-1.3123</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9773</v>
+        <v>-1.3263</v>
       </c>
       <c r="F25" t="n">
-        <v>0.971</v>
+        <v>0.014</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9457</v>
+        <v>-2.4156</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6599</v>
+        <v>-1.8594</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2858</v>
+        <v>-0.5561</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7167</v>
+        <v>-1.8862</v>
       </c>
       <c r="K25" t="n">
-        <v>0.103</v>
+        <v>-2.0308</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8196</v>
+        <v>0.1446</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.229</v>
+        <v>-0.5294</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7629</v>
+        <v>0.1714</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5339</v>
+        <v>-0.7008</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.2985</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9702</v>
+        <v>3.2985</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0606</v>
+        <v>0.5824</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2905</v>
+        <v>0.2778</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2299</v>
+        <v>0.3045</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-2.7776</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-3.0597</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.5569</v>
+        <v>-1.7966</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.8709</v>
+        <v>-3.2713</v>
       </c>
       <c r="F26" t="n">
-        <v>1.314</v>
+        <v>1.4747</v>
       </c>
       <c r="G26" t="n">
         <v>-2.2159</v>
@@ -2482,13 +2482,13 @@
         <v>1.7463</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8919</v>
+        <v>0.6522</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.4015</v>
       </c>
       <c r="U26" t="n">
-        <v>0.09</v>
+        <v>0.2507</v>
       </c>
       <c r="V26" t="n">
         <v>-1.9791</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>28.3498</v>
+        <v>29.68439999999999</v>
       </c>
       <c r="E27" t="n">
         <v>18.6754</v>
       </c>
       <c r="F27" t="n">
-        <v>9.674200000000001</v>
+        <v>11.009</v>
       </c>
       <c r="G27" t="n">
         <v>10.5972</v>
@@ -2536,7 +2536,7 @@
         <v>16.1719</v>
       </c>
       <c r="K27" t="n">
-        <v>1.1288</v>
+        <v>1.128799999999999</v>
       </c>
       <c r="L27" t="n">
         <v>15.0434</v>
@@ -2548,7 +2548,7 @@
         <v>-4.7123</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.8622000000000002</v>
+        <v>-0.8622000000000001</v>
       </c>
       <c r="P27" t="n">
         <v>20.3734</v>
@@ -2560,13 +2560,13 @@
         <v>27.1646</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.2431</v>
+        <v>-0.9083999999999998</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.7742000000000001</v>
+        <v>-0.7742</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.4689</v>
+        <v>-0.1345</v>
       </c>
       <c r="V27" t="n">
         <v>-0.3776999999999997</v>
